--- a/output/topology_excel/12448.xlsx
+++ b/output/topology_excel/12448.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -704,10 +704,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -748,10 +748,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="F17" t="n">
         <v>11</v>
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
@@ -839,7 +839,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="F19" t="n">
         <v>11</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>430</v>
+        <v>235</v>
       </c>
       <c r="F20" t="n">
-        <v>396</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B21" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>387</v>
+        <v>137</v>
       </c>
       <c r="F21" t="n">
         <v>11</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>106</v>
+        <v>419</v>
       </c>
       <c r="F22" t="n">
         <v>11</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>168</v>
+        <v>387</v>
       </c>
       <c r="F23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,15 +960,15 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>441</v>
+        <v>106</v>
       </c>
       <c r="F24" t="n">
-        <v>271</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
@@ -993,7 +993,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>340</v>
+        <v>419</v>
       </c>
       <c r="F26" t="n">
-        <v>177</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -1015,7 +1015,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="F27" t="n">
         <v>11</v>
@@ -1037,7 +1037,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,7 +1048,7 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
@@ -1059,7 +1059,7 @@
         <v>4</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>183</v>
+        <v>385</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="F30" t="n">
         <v>11</v>
@@ -1103,7 +1103,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="F31" t="n">
         <v>11</v>
@@ -1125,7 +1125,7 @@
         <v>5</v>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>162</v>
+        <v>314</v>
       </c>
       <c r="F32" t="n">
         <v>11</v>
@@ -1144,10 +1144,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>111</v>
+        <v>340</v>
       </c>
       <c r="F33" t="n">
-        <v>11</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="F34" t="n">
         <v>11</v>
@@ -1191,7 +1191,7 @@
         <v>6</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1202,10 +1202,10 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>183</v>
+        <v>61</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -1213,7 +1213,7 @@
         <v>7</v>
       </c>
       <c r="B36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F36" t="n">
         <v>11</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B37" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>1</v>
       </c>
       <c r="E37" t="n">
-        <v>235</v>
+        <v>111</v>
       </c>
       <c r="F37" t="n">
         <v>11</v>
@@ -1254,10 +1254,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B38" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="F38" t="n">
         <v>11</v>
@@ -1276,10 +1276,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1290,18 +1290,18 @@
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>62</v>
+        <v>183</v>
       </c>
       <c r="F39" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B40" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1312,18 +1312,18 @@
         <v>1</v>
       </c>
       <c r="E40" t="n">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="F40" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B41" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>314</v>
+        <v>123</v>
       </c>
       <c r="F41" t="n">
         <v>11</v>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B42" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1359,15 +1359,15 @@
         <v>137</v>
       </c>
       <c r="F42" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B43" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>61</v>
+        <v>123</v>
       </c>
       <c r="F43" t="n">
         <v>22</v>
@@ -1386,32 +1386,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B44" t="n">
+        <v>16</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>168</v>
+      </c>
+      <c r="F44" t="n">
         <v>13</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>160</v>
-      </c>
-      <c r="F44" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1422,19 +1422,19 @@
         <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="F45" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" t="n">
         <v>14</v>
       </c>
-      <c r="B46" t="n">
-        <v>16</v>
-      </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -1444,10 +1444,98 @@
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="F46" t="n">
-        <v>22</v>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" t="n">
+        <v>15</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>157</v>
+      </c>
+      <c r="F47" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>203</v>
+      </c>
+      <c r="F48" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>15</v>
+      </c>
+      <c r="B49" t="n">
+        <v>17</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>203</v>
+      </c>
+      <c r="F49" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2</v>
+      </c>
+      <c r="B50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>192</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/12448.xlsx
+++ b/output/topology_excel/12448.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
         <v>340</v>
       </c>
       <c r="F33" t="n">
-        <v>177</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
@@ -1447,7 +1447,7 @@
         <v>183</v>
       </c>
       <c r="F46" t="n">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
